--- a/data/bonds/USBonds10YR.xlsx
+++ b/data/bonds/USBonds10YR.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="USGG10YR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="USbond" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +429,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trade Price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Log_return</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Z-Score</t>
         </is>
@@ -452,338 +461,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2005</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>34699</v>
       </c>
       <c r="C2" t="n">
-        <v>4.277725390625002</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>250.9685</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.215184414638078</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2006</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>35064</v>
       </c>
       <c r="C3" t="n">
-        <v>4.784476538461537</v>
+        <v>296.9053</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1185</v>
+        <v>1995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1695967213062147</v>
+        <v>0.1681</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.170326922332059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2007</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>35430</v>
       </c>
       <c r="C4" t="n">
-        <v>4.624893103448272</v>
+        <v>305.0219</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0334</v>
+        <v>1996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2532742051403221</v>
+        <v>0.027</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.1909961110168601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2008</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>35795</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6381393129771</v>
+        <v>334.4197</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2134</v>
+        <v>1997</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.754372077163868</v>
+        <v>0.092</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8967855840056752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2009</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>36160</v>
       </c>
       <c r="C6" t="n">
-        <v>3.240329501915708</v>
+        <v>367.8765</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1093</v>
+        <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4645704745102506</v>
+        <v>0.0954</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.953684934206854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2010</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>36525</v>
       </c>
       <c r="C7" t="n">
-        <v>3.193982758620692</v>
+        <v>358.8676</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0143</v>
+        <v>1999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2001021531644903</v>
+        <v>-0.0248</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.057874446434819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2011</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>36891</v>
       </c>
       <c r="C8" t="n">
-        <v>2.759816923076925</v>
+        <v>407.2527</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1359</v>
+        <v>2000</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5386216044870635</v>
+        <v>0.1265</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.474146637517636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2012</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>37256</v>
       </c>
       <c r="C9" t="n">
-        <v>1.784344444444445</v>
+        <v>434.6658</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3535</v>
+        <v>2001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.144393254222195</v>
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4466113132963492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2013</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>37621</v>
       </c>
       <c r="C10" t="n">
-        <v>2.33465900383142</v>
+        <v>485.2583</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3084</v>
+        <v>2002</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6982549762910557</v>
+        <v>0.1101</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.19969094831195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2014</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>37986</v>
       </c>
       <c r="C11" t="n">
-        <v>2.529037164750958</v>
+        <v>496.2585</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0833</v>
+        <v>2003</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07160424855494353</v>
+        <v>0.0224</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.2679775848184549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2015</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>38352</v>
       </c>
       <c r="C12" t="n">
-        <v>2.131300000000001</v>
+        <v>513.7882</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1573</v>
+        <v>2004</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5981965737165296</v>
+        <v>0.0347</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.06213581791419051</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2016</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>38717</v>
       </c>
       <c r="C13" t="n">
-        <v>1.836771264367816</v>
+        <v>528.1529</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1382</v>
+        <v>2005</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5450245217406977</v>
+        <v>0.0276</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1809550492166521</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2017</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>39082</v>
       </c>
       <c r="C14" t="n">
-        <v>2.326232692307693</v>
+        <v>544.6354</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2665</v>
+        <v>2006</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5816105271922415</v>
+        <v>0.0307</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1290762299155773</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2018</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>39447</v>
       </c>
       <c r="C15" t="n">
-        <v>2.907807662835251</v>
+        <v>593.6626</v>
       </c>
       <c r="D15" t="n">
-        <v>0.25</v>
+        <v>2007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.535676555590083</v>
+        <v>0.0862</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7997219866036643</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2019</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>39813</v>
       </c>
       <c r="C16" t="n">
-        <v>2.138363984674328</v>
+        <v>676.1224999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2646</v>
+        <v>2008</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8969065829838989</v>
+        <v>0.1301</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.534393008318884</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2020</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>40178</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8906187022900764</v>
+        <v>651.1459</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5835</v>
+        <v>2009</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.784684979585615</v>
+        <v>-0.0376</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.272083764839257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2021</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>40543</v>
       </c>
       <c r="C18" t="n">
-        <v>1.435065134099617</v>
+        <v>688.9988</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6113</v>
+        <v>2010</v>
       </c>
       <c r="E18" t="n">
-        <v>1.541491339824012</v>
+        <v>0.0565</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3026894274933675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2022</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>40908</v>
       </c>
       <c r="C19" t="n">
-        <v>2.950227692307694</v>
+        <v>755.2207</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0558</v>
+        <v>2011</v>
       </c>
       <c r="E19" t="n">
-        <v>2.778924696015491</v>
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.893438563405606</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>41274</v>
       </c>
       <c r="C20" t="n">
-        <v>3.955332307692307</v>
+        <v>770.122</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3407</v>
+        <v>2012</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7881742055486143</v>
+        <v>0.0195</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3165093835194603</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>41639</v>
+      </c>
+      <c r="C21" t="n">
+        <v>749.6852</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.093018162735547</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>42004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>786.5907999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1621145622904551</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>42369</v>
+      </c>
+      <c r="C23" t="n">
+        <v>792.9698</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.5072895577234127</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>42735</v>
+      </c>
+      <c r="C24" t="n">
+        <v>801.122</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.4721458414226846</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>43100</v>
+      </c>
+      <c r="C25" t="n">
+        <v>819.5388</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.2629570539183509</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>43465</v>
+      </c>
+      <c r="C26" t="n">
+        <v>826.3887</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.5039425371233434</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>43830</v>
+      </c>
+      <c r="C27" t="n">
+        <v>882.7831</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4616729059966612</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C28" t="n">
+        <v>953.236</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6424120184004053</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="C29" t="n">
+        <v>931.3469</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.0232</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.031098281634264</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>44926</v>
+      </c>
+      <c r="C30" t="n">
+        <v>813.899</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1348</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-2.898735776472956</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="C31" t="n">
+        <v>848.7190000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.05835692368830568</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C32" t="n">
+        <v>854.2143</v>
+      </c>
+      <c r="D32" t="n">
         <v>2024</v>
       </c>
-      <c r="C21" t="n">
-        <v>4.20402375478927</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0629</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.01481315639227498</v>
+      <c r="E32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.5340657225239674</v>
       </c>
     </row>
   </sheetData>
